--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/felmera.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/felmera.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="melilith" sheetId="1" r:id="rId3"/>
+    <sheet name="melilith" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -199,7 +199,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">これらの絵には、私が直々にナンバリングを施しましょう。あなたの持っているそのジャーナルに、大切に保管してください。</t>
@@ -221,48 +221,6 @@
   </si>
   <si>
     <t xml:space="preserve">give_sketch_reward</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">艺术当然不是爆炸之类的东西！它存在于细致的笔触，慢慢干燥的颜料，以及柔和的凝视中。遗憾的是，这座城镇上的俗人恐怕穷且一生也无法理解。
-都怪约格，让现在的绘画界都变了。如今「卖不出去」的画都没了价值，画家们就都随波逐流的去画些流行又低俗的画。鲁米艾斯特也要完蛋啦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想让你画画</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想让你帮忙鉴定古画</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我已经决定封笔了，至少在约格退出绘画界前都不再会画画…你还是去找其他画家吧。约格…自从他当上公会会长后就变了个人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉴定古画？…听着是让人挺感兴趣。旧时代的画里总会有一些能唤起我内心深处热情的的东西。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果你找到古旧的素描，就拿到我这里来吧。也许我能帮上你的忙。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的，就让我来鉴定一下。很快就好，你稍等一下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯，是还不错……不过遗憾的是没有什么特别珍贵的画。要是又找到了旧画就再拿来让我看看吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这是！
-这应该只是个无名画家的作品…但为什么这幅画却给我一种如此震撼的感觉？！
-这是…一部特别的作品，让我来加上编号吧。请好好保管在你的那个日志里。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这是！
-这些珍贵的画到底是在哪里找到的？不，那种事也都无所谓了。这幅画简直撼动了我的灵魂。
-让我亲自给这些画作编号吧。请好好保管在你的那个日志里。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请收下这个。呵呵，想起你给我看的那些无名的素描，我就忍不住想画画了！</t>
   </si>
 </sst>
 </file>
@@ -283,25 +241,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -315,7 +273,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -341,7 +299,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -350,62 +308,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -419,13 +377,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -601,25 +559,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,24 +612,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="113.4">
-      <c r="H10" s="1">
+    <row r="10" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -680,24 +638,21 @@
       <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" ht="13.8">
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" ht="13.8">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="5" t="s">
@@ -706,18 +661,15 @@
       <c r="J12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" ht="13.8">
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
@@ -726,11 +678,8 @@
       <c r="J13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" ht="12.8">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
@@ -741,7 +690,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
@@ -749,16 +698,16 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="46.25">
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I18" s="5" t="s">
@@ -767,22 +716,19 @@
       <c r="J18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="57.45">
-      <c r="H23" s="1">
+    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -791,11 +737,8 @@
       <c r="J23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" ht="13.8">
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
@@ -805,7 +748,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" ht="13.8">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
@@ -815,22 +758,22 @@
       <c r="I25" s="5"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" ht="13.8">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="5"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" ht="13.8">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" ht="13.8">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -839,22 +782,19 @@
       <c r="J28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" ht="35.05">
-      <c r="H32" s="1">
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I32" s="5" t="s">
@@ -863,11 +803,8 @@
       <c r="J32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
@@ -878,8 +815,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" ht="35.05">
-      <c r="H34" s="1">
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -888,22 +825,19 @@
       <c r="J34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" ht="12.8">
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" ht="91">
-      <c r="H39" s="1">
+    <row r="39" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -912,11 +846,8 @@
       <c r="J39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" ht="13.8">
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
@@ -928,18 +859,18 @@
       </c>
       <c r="I40" s="5"/>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" ht="97.75">
-      <c r="H44" s="1">
+    <row r="44" customFormat="false" ht="97.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -948,11 +879,8 @@
       <c r="J44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" ht="12.8">
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
@@ -960,18 +888,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" ht="32.8">
-      <c r="H51" s="1">
+    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -980,11 +908,8 @@
       <c r="J51" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" ht="12.8">
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D53" s="1" t="s">
         <v>42</v>
       </c>
@@ -992,19 +917,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H16:H1048576 H4:H13 I14:I15">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/felmera.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/felmera.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="melilith" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="melilith" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -199,7 +199,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">これらの絵には、私が直々にナンバリングを施しましょう。あなたの持っているそのジャーナルに、大切に保管してください。</t>
@@ -221,6 +221,48 @@
   </si>
   <si>
     <t xml:space="preserve">give_sketch_reward</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">艺术当然不是爆炸之类的东西！它存在于细致的笔触，慢慢干燥的颜料，以及柔和的凝视中。遗憾的是，这座城镇上的俗人恐怕穷且一生也无法理解。
+都怪约格，让现在的绘画界都变了。如今「卖不出去」的画都没了价值，画家们就都随波逐流的去画些流行又低俗的画。鲁米艾斯特也要完蛋啦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想让你画画</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想让你帮忙鉴定古画</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我已经决定封笔了，至少在约格退出绘画界前都不再会画画…你还是去找其他画家吧。约格…自从他当上公会会长后就变了个人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉴定古画？…听着是让人挺感兴趣。旧时代的画里总会有一些能唤起我内心深处热情的的东西。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果你找到古旧的素描，就拿到我这里来吧。也许我能帮上你的忙。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，就让我来鉴定一下。很快就好，你稍等一下。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯，是还不错……不过遗憾的是没有什么特别珍贵的画。要是又找到了旧画就再拿来让我看看吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这是！
+这应该只是个无名画家的作品…但为什么这幅画却给我一种如此震撼的感觉？！
+这是…一部特别的作品，让我来加上编号吧。请好好保管在你的那个日志里。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这是！
+这些珍贵的画到底是在哪里找到的？不，那种事也都无所谓了。这幅画简直撼动了我的灵魂。
+让我亲自给这些画作编号吧。请好好保管在你的那个日志里。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请收下这个。呵呵，想起你给我看的那些无名的素描，我就忍不住想画画了！</t>
   </si>
 </sst>
 </file>
@@ -241,25 +283,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -273,7 +315,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -299,7 +341,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -308,62 +350,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -377,13 +419,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -559,25 +601,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,24 +654,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H10" s="1" t="n">
+    <row r="10" ht="113.4">
+      <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -638,21 +680,24 @@
       <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" ht="13.8">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="13.8">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="1">
         <v>2</v>
       </c>
       <c r="I12" s="5" t="s">
@@ -661,15 +706,18 @@
       <c r="J12" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="13.8">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="1">
         <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
@@ -678,8 +726,11 @@
       <c r="J13" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
@@ -690,7 +741,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
@@ -698,16 +749,16 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="46.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="1">
         <v>4</v>
       </c>
       <c r="I18" s="5" t="s">
@@ -716,19 +767,22 @@
       <c r="J18" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H23" s="1" t="n">
+    <row r="23" ht="57.45">
+      <c r="H23" s="1">
         <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -737,8 +791,11 @@
       <c r="J23" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" ht="13.8">
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
@@ -748,7 +805,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="13.8">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
@@ -758,22 +815,22 @@
       <c r="I25" s="5"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="13.8">
       <c r="I26" s="5"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="13.8">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="13.8">
       <c r="D28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="1">
         <v>6</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -782,19 +839,22 @@
       <c r="J28" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="1" t="n">
+    <row r="32" ht="35.05">
+      <c r="H32" s="1">
         <v>7</v>
       </c>
       <c r="I32" s="5" t="s">
@@ -803,8 +863,11 @@
       <c r="J32" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
@@ -815,8 +878,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H34" s="1" t="n">
+    <row r="34" ht="35.05">
+      <c r="H34" s="1">
         <v>8</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -825,19 +888,22 @@
       <c r="J34" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
       <c r="B35" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="1" t="n">
+    <row r="39" ht="91">
+      <c r="H39" s="1">
         <v>9</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -846,8 +912,11 @@
       <c r="J39" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" ht="13.8">
       <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
@@ -859,18 +928,18 @@
       </c>
       <c r="I40" s="5"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="B41" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="97.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H44" s="1" t="n">
+    <row r="44" ht="97.75">
+      <c r="H44" s="1">
         <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -879,8 +948,11 @@
       <c r="J44" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" ht="12.8">
       <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
@@ -888,18 +960,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="B46" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H51" s="1" t="n">
+    <row r="51" ht="32.8">
+      <c r="H51" s="1">
         <v>11</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -908,8 +980,11 @@
       <c r="J51" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" ht="12.8">
       <c r="D53" s="1" t="s">
         <v>42</v>
       </c>
@@ -917,19 +992,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="B54" s="1" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H16:H1048576 H4:H13 I14:I15">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
